--- a/source_environmental_conditions.xlsx
+++ b/source_environmental_conditions.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t xml:space="preserve">parameter</t>
   </si>
@@ -62,6 +62,9 @@
   </si>
   <si>
     <t xml:space="preserve">s0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sa0</t>
   </si>
   <si>
     <t xml:space="preserve">supper</t>
@@ -195,7 +198,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -217,7 +220,11 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -412,7 +419,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B1048576"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18.96"/>
@@ -446,7 +453,7 @@
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="6" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -454,7 +461,7 @@
       <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="6" t="n">
         <v>50</v>
       </c>
     </row>
@@ -462,7 +469,7 @@
       <c r="A6" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -470,7 +477,7 @@
       <c r="A7" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="6" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -478,7 +485,7 @@
       <c r="A8" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="6" t="n">
         <v>0.998</v>
       </c>
     </row>
@@ -486,15 +493,15 @@
       <c r="A9" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="1" t="n">
-        <v>0.998</v>
+      <c r="B9" s="6" t="n">
+        <v>1.015</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="6" t="n">
         <v>0.998</v>
       </c>
     </row>
@@ -502,7 +509,7 @@
       <c r="A11" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="6" t="n">
         <v>2.5</v>
       </c>
     </row>
@@ -510,7 +517,7 @@
       <c r="A12" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="6" t="n">
         <v>15</v>
       </c>
     </row>
@@ -518,63 +525,70 @@
       <c r="A13" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="1" t="n">
-        <v>0</v>
+      <c r="B13" s="6" t="n">
+        <v>22.0725</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>16</v>
+      <c r="B14" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="6" t="s">
         <v>17</v>
-      </c>
-      <c r="B15" s="1" t="n">
-        <v>20</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>19</v>
+      <c r="B16" s="6" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="5" t="s">
         <v>20</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" s="5" t="s">
         <v>22</v>
-      </c>
-      <c r="B18" s="1" t="n">
-        <v>20</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="6" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" s="6" t="n">
         <v>-1.5E-005</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4"/>
-      <c r="B20" s="1"/>
-    </row>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="4"/>
+      <c r="B21" s="1"/>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
